--- a/Excel_usuarios/Usuarios.xlsx
+++ b/Excel_usuarios/Usuarios.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Indurex\Documents\GitHub\vehiculos_ecohabitat\Excel_usuarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA196358-981C-4954-9F80-666303F2E934}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C09554D9-EB08-432A-9533-1188062E6EDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1040" yWindow="1010" windowWidth="16200" windowHeight="9150" xr2:uid="{3E0C0804-3B11-475D-9E2A-D27248C45737}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3E0C0804-3B11-475D-9E2A-D27248C45737}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="118">
   <si>
     <t>Raquel</t>
   </si>
@@ -361,6 +361,39 @@
   </si>
   <si>
     <t>a7acc211-9d72-4feb-b8b1-be0f7545756e</t>
+  </si>
+  <si>
+    <t>rafa@agroforex.com</t>
+  </si>
+  <si>
+    <t>Rafaagroforex</t>
+  </si>
+  <si>
+    <t>Carlos Riaño</t>
+  </si>
+  <si>
+    <t>Carlosecohabitat</t>
+  </si>
+  <si>
+    <t>Saloua</t>
+  </si>
+  <si>
+    <t>administracion@agroforex.com</t>
+  </si>
+  <si>
+    <t>Salouaecohabitat</t>
+  </si>
+  <si>
+    <t>7de6580e-c0fb-42d2-a2eb-b7747b314686</t>
+  </si>
+  <si>
+    <t>carlos.riano@ecohabitatiberico.com</t>
+  </si>
+  <si>
+    <t>d8694fae-85a8-4aa9-95dc-4a66f2e8a3c4</t>
+  </si>
+  <si>
+    <t>40b0bd4f-81fc-4d49-91b1-a73b3ca33dce</t>
   </si>
 </sst>
 </file>
@@ -806,17 +839,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C6217C1-14CE-4305-943F-93311776B0D0}">
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.26953125" customWidth="1"/>
-    <col min="2" max="2" width="33.6328125" customWidth="1"/>
-    <col min="3" max="3" width="20.453125" customWidth="1"/>
-    <col min="4" max="4" width="20.7265625" customWidth="1"/>
-    <col min="5" max="5" width="37.08984375" customWidth="1"/>
+    <col min="1" max="1" width="21.28515625" customWidth="1"/>
+    <col min="2" max="2" width="33.5703125" customWidth="1"/>
+    <col min="3" max="3" width="29.85546875" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" customWidth="1"/>
+    <col min="5" max="5" width="37.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -833,7 +866,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -850,7 +883,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -867,7 +900,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>30</v>
       </c>
@@ -884,7 +917,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>61</v>
       </c>
@@ -901,7 +934,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>96</v>
       </c>
@@ -918,7 +951,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>32</v>
       </c>
@@ -935,7 +968,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>101</v>
       </c>
@@ -950,6 +983,57 @@
       </c>
       <c r="E8" t="s">
         <v>106</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C9" t="s">
+        <v>108</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E9" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>109</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C10" t="s">
+        <v>110</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E10" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>111</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C11" t="s">
+        <v>113</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E11" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -961,6 +1045,9 @@
     <hyperlink ref="B6" r:id="rId5" xr:uid="{6AC95B51-4E25-48B9-8574-061D967E044F}"/>
     <hyperlink ref="B8" r:id="rId6" xr:uid="{E2D99DA3-FCAD-458A-B37F-C30F6FAD7B8C}"/>
     <hyperlink ref="B7" r:id="rId7" xr:uid="{F0AC3F92-4F97-4C6A-81E2-0CF036FB9712}"/>
+    <hyperlink ref="B9" r:id="rId8" xr:uid="{460521B3-F523-4F36-9FA7-468F5F7A142D}"/>
+    <hyperlink ref="B10" r:id="rId9" xr:uid="{EF04E834-E1C6-4F5F-AD34-713A387F2107}"/>
+    <hyperlink ref="B11" r:id="rId10" xr:uid="{B91BE01E-7318-457C-96A0-E5D16B56B66C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -969,16 +1056,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93716D6F-2DA0-493F-8F08-BD7C6B16EBA2}">
   <dimension ref="A1:E37"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.1796875" customWidth="1"/>
-    <col min="2" max="2" width="24.7265625" customWidth="1"/>
-    <col min="3" max="3" width="33.7265625" customWidth="1"/>
-    <col min="4" max="4" width="37.26953125" customWidth="1"/>
-    <col min="6" max="6" width="14.453125" customWidth="1"/>
+    <col min="1" max="1" width="5.140625" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="33.7109375" customWidth="1"/>
+    <col min="4" max="4" width="37.28515625" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>13</v>
       </c>
@@ -995,7 +1082,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
         <v>1</v>
       </c>
@@ -1012,7 +1099,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
         <v>2</v>
       </c>
@@ -1029,7 +1116,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <v>3</v>
       </c>
@@ -1046,7 +1133,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>4</v>
       </c>
@@ -1063,7 +1150,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>5</v>
       </c>
@@ -1080,7 +1167,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>6</v>
       </c>
@@ -1097,7 +1184,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>7</v>
       </c>
@@ -1114,7 +1201,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>8</v>
       </c>
@@ -1131,7 +1218,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>9</v>
       </c>
@@ -1148,7 +1235,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>10</v>
       </c>
@@ -1165,7 +1252,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>11</v>
       </c>
@@ -1182,7 +1269,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>12</v>
       </c>
@@ -1199,7 +1286,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="8">
         <v>13</v>
       </c>
@@ -1216,7 +1303,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
         <v>14</v>
       </c>
@@ -1233,7 +1320,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
         <v>15</v>
       </c>
@@ -1250,7 +1337,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="8">
         <v>16</v>
       </c>
@@ -1267,7 +1354,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="8">
         <v>17</v>
       </c>
@@ -1284,7 +1371,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="8">
         <v>18</v>
       </c>
@@ -1301,7 +1388,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="8">
         <v>19</v>
       </c>
@@ -1318,7 +1405,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="8">
         <v>20</v>
       </c>
@@ -1335,7 +1422,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="8">
         <v>21</v>
       </c>
@@ -1352,7 +1439,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="8">
         <v>22</v>
       </c>
@@ -1369,7 +1456,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="8">
         <v>23</v>
       </c>
@@ -1386,7 +1473,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="8">
         <v>24</v>
       </c>
@@ -1403,7 +1490,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="8">
         <v>25</v>
       </c>
@@ -1420,7 +1507,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="8">
         <v>26</v>
       </c>
@@ -1437,7 +1524,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="8">
         <v>27</v>
       </c>
@@ -1454,7 +1541,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="8">
         <v>28</v>
       </c>
@@ -1471,7 +1558,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="8">
         <v>29</v>
       </c>
@@ -1488,7 +1575,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="8">
         <v>30</v>
       </c>
@@ -1505,7 +1592,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="8">
         <v>31</v>
       </c>
@@ -1522,7 +1609,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="8">
         <v>32</v>
       </c>
@@ -1539,7 +1626,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="8">
         <v>33</v>
       </c>
@@ -1556,7 +1643,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="8">
         <v>34</v>
       </c>
@@ -1573,7 +1660,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="8">
         <v>35</v>
       </c>
@@ -1590,7 +1677,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="8">
         <v>36</v>
       </c>

--- a/Excel_usuarios/Usuarios.xlsx
+++ b/Excel_usuarios/Usuarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Indurex\Documents\GitHub\vehiculos_ecohabitat\Excel_usuarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C09554D9-EB08-432A-9533-1188062E6EDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F245478C-D06A-4603-8119-81F1AC49A211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3E0C0804-3B11-475D-9E2A-D27248C45737}"/>
   </bookViews>
